--- a/Result/profitability/8940.xlsx
+++ b/Result/profitability/8940.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4287500000000001</v>
+        <v>0.4187500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>48.52875</v>
+        <v>48.00375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4475000000000001</v>
+        <v>0.30625</v>
       </c>
       <c r="N3" t="n">
-        <v>48.54375</v>
+        <v>47.05125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3025000000000001</v>
+        <v>0.09625000000000007</v>
       </c>
       <c r="N4" t="n">
-        <v>46.445</v>
+        <v>44.74</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2762500000000001</v>
+        <v>0.26375</v>
       </c>
       <c r="N5" t="n">
-        <v>46.37375</v>
+        <v>45.77375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.39</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3612500000000001</v>
+        <v>0.4312500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>46.9775</v>
+        <v>47.95125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,16 +1264,16 @@
         <v>-0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4525000000000001</v>
+        <v>0.3375000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>48.16500000000001</v>
+        <v>46.75750000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3425</v>
+        <v>0.1262500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>46.20875</v>
+        <v>44.6275</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.17625</v>
+        <v>0.1762500000000001</v>
       </c>
       <c r="N10" t="n">
         <v>45.63625</v>
@@ -1772,7 +1772,7 @@
         <v>0.09</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2075</v>
+        <v>0.2075000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>45.93125000000001</v>
@@ -2026,7 +2026,7 @@
         <v>0.18</v>
       </c>
       <c r="M13" t="n">
-        <v>0.14125</v>
+        <v>0.1412500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>46.64125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8940</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>302</v>
+      </c>
+      <c r="D75" t="n">
+        <v>179</v>
+      </c>
+      <c r="E75" t="n">
+        <v>123</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-37</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-12.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.24125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>46.9675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.291044776119403</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-12.65</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2374249249249248</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3448275862068968</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.799999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1056570548095971</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
